--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1376,7 +1376,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="25">
       <c r="A4" s="35" t="inlineStr">
         <is>
@@ -1438,12 +1437,12 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>Card (prompt)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t>Log</t>
         </is>
@@ -2003,22 +2002,22 @@
       </c>
       <c r="F14" s="37" t="inlineStr">
         <is>
-          <t>Identity provider spike</t>
+          <t>Native AuthProvider implementation</t>
         </is>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>Decision D4 resolved; OIDC PKCE flow working end to end</t>
+          <t>AuthProvider interface + NativeAuthProvider (Argon2id, sessions, rate limiting) per ADR-002; Auth0 deferred, interface keeps swap-in possible later</t>
         </is>
       </c>
       <c r="H14" s="36" t="inlineStr">
         <is>
-          <t>A test user can sign in and receive a token</t>
+          <t>Register/login/authenticated-route/logout/reset-initiation all pass against NativeAuthProvider; test proves no module imports NativeAuthProvider directly except via the interface</t>
         </is>
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>No password storage anywhere in our systems</t>
+          <t>Argon2id hashing, no plaintext/bcrypt; login+reset rate-limited from this card; sessions revocable server-side; see docs/adr/ADR-002-authentication-provider.md</t>
         </is>
       </c>
       <c r="J14" s="43" t="inlineStr">
@@ -2027,7 +2026,11 @@
         </is>
       </c>
       <c r="K14" s="43" t="n"/>
-      <c r="L14" s="43" t="n"/>
+      <c r="L14" s="43" t="inlineStr">
+        <is>
+          <t>Revised per ADR-002 (2026-09-07): was 'Identity provider spike / OIDC PKCE'. Founder decision: native auth now, Auth0-ready interface, Auth0 wired in later.</t>
+        </is>
+      </c>
       <c r="M14" s="44" t="inlineStr">
         <is>
           <t>D010</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1344,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:O180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="24" min="1" max="1"/>
@@ -1360,6 +1360,7 @@
     <col width="30" customWidth="1" style="24" min="12" max="12"/>
     <col width="14" customWidth="1" style="25" min="13" max="13"/>
     <col width="14" customWidth="1" style="25" min="14" max="14"/>
+    <col width="22" customWidth="1" style="25" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="25">
@@ -1447,6 +1448,11 @@
           <t>Log</t>
         </is>
       </c>
+      <c r="O4" s="24" t="inlineStr">
+        <is>
+          <t>Est. Duration (AI session)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.85" customHeight="1" s="25">
       <c r="A5" s="36" t="n">
@@ -1506,6 +1512,11 @@
           <t>D001</t>
         </is>
       </c>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="25">
       <c r="A6" s="36" t="n">
@@ -1565,6 +1576,11 @@
           <t>D002</t>
         </is>
       </c>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.85" customHeight="1" s="25">
       <c r="A7" s="36" t="n">
@@ -1624,6 +1640,11 @@
           <t>D003</t>
         </is>
       </c>
+      <c r="O7" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23.85" customHeight="1" s="25">
       <c r="A8" s="36" t="n">
@@ -1683,6 +1704,11 @@
           <t>D004</t>
         </is>
       </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.85" customHeight="1" s="25">
       <c r="A9" s="36" t="n">
@@ -1742,6 +1768,11 @@
           <t>D005</t>
         </is>
       </c>
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.85" customHeight="1" s="25">
       <c r="A10" s="36" t="n">
@@ -1801,6 +1832,11 @@
           <t>D006</t>
         </is>
       </c>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="25">
       <c r="A11" s="36" t="n">
@@ -1860,6 +1896,11 @@
           <t>D007</t>
         </is>
       </c>
+      <c r="O11" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="36" t="n">
@@ -1919,6 +1960,11 @@
           <t>D008</t>
         </is>
       </c>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.85" customHeight="1" s="25">
       <c r="A13" s="36" t="n">
@@ -1978,6 +2024,11 @@
           <t>D009</t>
         </is>
       </c>
+      <c r="O13" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="25">
       <c r="A14" s="36" t="n">
@@ -2041,6 +2092,11 @@
           <t>D010</t>
         </is>
       </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="25">
       <c r="A15" s="36" t="n">
@@ -2100,6 +2156,11 @@
           <t>D011</t>
         </is>
       </c>
+      <c r="O15" s="24" t="inlineStr">
+        <is>
+          <t>1.0h</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="25">
       <c r="A16" s="45" t="n">
@@ -2159,6 +2220,11 @@
           <t>D012</t>
         </is>
       </c>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.85" customHeight="1" s="25">
       <c r="A17" s="36" t="n">
@@ -2218,6 +2284,11 @@
           <t>D013</t>
         </is>
       </c>
+      <c r="O17" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="36" t="n">
@@ -2277,6 +2348,11 @@
           <t>D014</t>
         </is>
       </c>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.85" customHeight="1" s="25">
       <c r="A19" s="36" t="n">
@@ -2336,6 +2412,11 @@
           <t>D015</t>
         </is>
       </c>
+      <c r="O19" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.85" customHeight="1" s="25">
       <c r="A20" s="36" t="n">
@@ -2395,6 +2476,11 @@
           <t>D016</t>
         </is>
       </c>
+      <c r="O20" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1" s="25">
       <c r="A21" s="36" t="n">
@@ -2454,6 +2540,11 @@
           <t>D017</t>
         </is>
       </c>
+      <c r="O21" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="25">
       <c r="A22" s="36" t="n">
@@ -2513,6 +2604,11 @@
           <t>D018</t>
         </is>
       </c>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.85" customHeight="1" s="25">
       <c r="A23" s="36" t="n">
@@ -2572,6 +2668,11 @@
           <t>D019</t>
         </is>
       </c>
+      <c r="O23" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.85" customHeight="1" s="25">
       <c r="A24" s="36" t="n">
@@ -2631,6 +2732,11 @@
           <t>D020</t>
         </is>
       </c>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1" s="25">
       <c r="A25" s="36" t="n">
@@ -2690,6 +2796,11 @@
           <t>D021</t>
         </is>
       </c>
+      <c r="O25" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1" s="25">
       <c r="A26" s="36" t="n">
@@ -2749,6 +2860,11 @@
           <t>D022</t>
         </is>
       </c>
+      <c r="O26" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.85" customHeight="1" s="25">
       <c r="A27" s="36" t="n">
@@ -2808,6 +2924,11 @@
           <t>D023</t>
         </is>
       </c>
+      <c r="O27" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1" s="25">
       <c r="A28" s="36" t="n">
@@ -2867,6 +2988,11 @@
           <t>D024</t>
         </is>
       </c>
+      <c r="O28" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.85" customHeight="1" s="25">
       <c r="A29" s="36" t="n">
@@ -2926,6 +3052,11 @@
           <t>D025</t>
         </is>
       </c>
+      <c r="O29" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.85" customHeight="1" s="25">
       <c r="A30" s="36" t="n">
@@ -2985,6 +3116,11 @@
           <t>D026</t>
         </is>
       </c>
+      <c r="O30" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1" s="25">
       <c r="A31" s="36" t="n">
@@ -3044,6 +3180,11 @@
           <t>D027</t>
         </is>
       </c>
+      <c r="O31" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.85" customHeight="1" s="25">
       <c r="A32" s="36" t="n">
@@ -3103,6 +3244,11 @@
           <t>D028</t>
         </is>
       </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.85" customHeight="1" s="25">
       <c r="A33" s="36" t="n">
@@ -3162,6 +3308,11 @@
           <t>D029</t>
         </is>
       </c>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="23.85" customHeight="1" s="25">
       <c r="A34" s="45" t="n">
@@ -3221,6 +3372,11 @@
           <t>D030</t>
         </is>
       </c>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="25">
       <c r="A35" s="36" t="n">
@@ -3280,6 +3436,11 @@
           <t>D031</t>
         </is>
       </c>
+      <c r="O35" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.85" customHeight="1" s="25">
       <c r="A36" s="36" t="n">
@@ -3339,6 +3500,11 @@
           <t>D032</t>
         </is>
       </c>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.85" customHeight="1" s="25">
       <c r="A37" s="36" t="n">
@@ -3398,6 +3564,11 @@
           <t>D033</t>
         </is>
       </c>
+      <c r="O37" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.85" customHeight="1" s="25">
       <c r="A38" s="36" t="n">
@@ -3457,6 +3628,11 @@
           <t>D034</t>
         </is>
       </c>
+      <c r="O38" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="25">
       <c r="A39" s="36" t="n">
@@ -3516,6 +3692,11 @@
           <t>D035</t>
         </is>
       </c>
+      <c r="O39" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.85" customHeight="1" s="25">
       <c r="A40" s="36" t="n">
@@ -3575,6 +3756,11 @@
           <t>D036</t>
         </is>
       </c>
+      <c r="O40" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.85" customHeight="1" s="25">
       <c r="A41" s="36" t="n">
@@ -3634,6 +3820,11 @@
           <t>D037</t>
         </is>
       </c>
+      <c r="O41" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="23.85" customHeight="1" s="25">
       <c r="A42" s="36" t="n">
@@ -3693,6 +3884,11 @@
           <t>D038</t>
         </is>
       </c>
+      <c r="O42" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="23.85" customHeight="1" s="25">
       <c r="A43" s="36" t="n">
@@ -3752,6 +3948,11 @@
           <t>D039</t>
         </is>
       </c>
+      <c r="O43" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="25">
       <c r="A44" s="36" t="n">
@@ -3811,6 +4012,11 @@
           <t>D040</t>
         </is>
       </c>
+      <c r="O44" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="25">
       <c r="A45" s="36" t="n">
@@ -3870,6 +4076,11 @@
           <t>D041</t>
         </is>
       </c>
+      <c r="O45" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="23.85" customHeight="1" s="25">
       <c r="A46" s="36" t="n">
@@ -3929,6 +4140,11 @@
           <t>D042</t>
         </is>
       </c>
+      <c r="O46" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="25">
       <c r="A47" s="36" t="n">
@@ -3988,6 +4204,11 @@
           <t>D043</t>
         </is>
       </c>
+      <c r="O47" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="23.85" customHeight="1" s="25">
       <c r="A48" s="45" t="n">
@@ -4047,6 +4268,11 @@
           <t>D044</t>
         </is>
       </c>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.85" customHeight="1" s="25">
       <c r="A49" s="36" t="n">
@@ -4106,6 +4332,11 @@
           <t>D045</t>
         </is>
       </c>
+      <c r="O49" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="23.85" customHeight="1" s="25">
       <c r="A50" s="36" t="n">
@@ -4165,6 +4396,11 @@
           <t>D046</t>
         </is>
       </c>
+      <c r="O50" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="25">
       <c r="A51" s="36" t="n">
@@ -4224,6 +4460,11 @@
           <t>D047</t>
         </is>
       </c>
+      <c r="O51" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="23.85" customHeight="1" s="25">
       <c r="A52" s="36" t="n">
@@ -4283,6 +4524,11 @@
           <t>D048</t>
         </is>
       </c>
+      <c r="O52" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="23.85" customHeight="1" s="25">
       <c r="A53" s="36" t="n">
@@ -4342,6 +4588,11 @@
           <t>D049</t>
         </is>
       </c>
+      <c r="O53" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="23.85" customHeight="1" s="25">
       <c r="A54" s="36" t="n">
@@ -4401,6 +4652,11 @@
           <t>D050</t>
         </is>
       </c>
+      <c r="O54" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.85" customHeight="1" s="25">
       <c r="A55" s="36" t="n">
@@ -4460,6 +4716,11 @@
           <t>D051</t>
         </is>
       </c>
+      <c r="O55" s="24" t="inlineStr">
+        <is>
+          <t>5.5h</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="25">
       <c r="A56" s="36" t="n">
@@ -4519,6 +4780,11 @@
           <t>D052</t>
         </is>
       </c>
+      <c r="O56" s="24" t="inlineStr">
+        <is>
+          <t>5.5h</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="23.85" customHeight="1" s="25">
       <c r="A57" s="36" t="n">
@@ -4578,6 +4844,11 @@
           <t>D053</t>
         </is>
       </c>
+      <c r="O57" s="24" t="inlineStr">
+        <is>
+          <t>5.5h</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="23.85" customHeight="1" s="25">
       <c r="A58" s="36" t="n">
@@ -4637,6 +4908,11 @@
           <t>D054</t>
         </is>
       </c>
+      <c r="O58" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.85" customHeight="1" s="25">
       <c r="A59" s="36" t="n">
@@ -4696,6 +4972,11 @@
           <t>D055</t>
         </is>
       </c>
+      <c r="O59" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="23.85" customHeight="1" s="25">
       <c r="A60" s="36" t="n">
@@ -4755,6 +5036,11 @@
           <t>D056</t>
         </is>
       </c>
+      <c r="O60" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="23.85" customHeight="1" s="25">
       <c r="A61" s="36" t="n">
@@ -4814,6 +5100,11 @@
           <t>D057</t>
         </is>
       </c>
+      <c r="O61" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="23.85" customHeight="1" s="25">
       <c r="A62" s="36" t="n">
@@ -4873,6 +5164,11 @@
           <t>D058</t>
         </is>
       </c>
+      <c r="O62" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="25">
       <c r="A63" s="36" t="n">
@@ -4932,6 +5228,11 @@
           <t>D059</t>
         </is>
       </c>
+      <c r="O63" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.85" customHeight="1" s="25">
       <c r="A64" s="36" t="n">
@@ -4991,6 +5292,11 @@
           <t>D060</t>
         </is>
       </c>
+      <c r="O64" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.85" customHeight="1" s="25">
       <c r="A65" s="36" t="n">
@@ -5050,6 +5356,11 @@
           <t>D061</t>
         </is>
       </c>
+      <c r="O65" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.85" customHeight="1" s="25">
       <c r="A66" s="45" t="n">
@@ -5109,6 +5420,11 @@
           <t>D062</t>
         </is>
       </c>
+      <c r="O66" s="24" t="inlineStr">
+        <is>
+          <t>6.0h</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.85" customHeight="1" s="25">
       <c r="A67" s="36" t="n">
@@ -5168,6 +5484,11 @@
           <t>D063</t>
         </is>
       </c>
+      <c r="O67" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.85" customHeight="1" s="25">
       <c r="A68" s="36" t="n">
@@ -5227,6 +5548,11 @@
           <t>D064</t>
         </is>
       </c>
+      <c r="O68" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="23.85" customHeight="1" s="25">
       <c r="A69" s="36" t="n">
@@ -5286,6 +5612,11 @@
           <t>D065</t>
         </is>
       </c>
+      <c r="O69" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="25">
       <c r="A70" s="36" t="n">
@@ -5345,6 +5676,11 @@
           <t>D066</t>
         </is>
       </c>
+      <c r="O70" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="25">
       <c r="A71" s="36" t="n">
@@ -5404,6 +5740,11 @@
           <t>D067</t>
         </is>
       </c>
+      <c r="O71" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="23.85" customHeight="1" s="25">
       <c r="A72" s="36" t="n">
@@ -5463,6 +5804,11 @@
           <t>D068</t>
         </is>
       </c>
+      <c r="O72" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="23.85" customHeight="1" s="25">
       <c r="A73" s="36" t="n">
@@ -5522,6 +5868,11 @@
           <t>D069</t>
         </is>
       </c>
+      <c r="O73" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="25">
       <c r="A74" s="36" t="n">
@@ -5581,6 +5932,11 @@
           <t>D070</t>
         </is>
       </c>
+      <c r="O74" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="25">
       <c r="A75" s="36" t="n">
@@ -5640,6 +5996,11 @@
           <t>D071</t>
         </is>
       </c>
+      <c r="O75" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="23.85" customHeight="1" s="25">
       <c r="A76" s="36" t="n">
@@ -5699,6 +6060,11 @@
           <t>D072</t>
         </is>
       </c>
+      <c r="O76" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="25">
       <c r="A77" s="36" t="n">
@@ -5758,6 +6124,11 @@
           <t>D073</t>
         </is>
       </c>
+      <c r="O77" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="23.85" customHeight="1" s="25">
       <c r="A78" s="36" t="n">
@@ -5817,6 +6188,11 @@
           <t>D074</t>
         </is>
       </c>
+      <c r="O78" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="23.85" customHeight="1" s="25">
       <c r="A79" s="36" t="n">
@@ -5876,6 +6252,11 @@
           <t>D075</t>
         </is>
       </c>
+      <c r="O79" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="23.85" customHeight="1" s="25">
       <c r="A80" s="36" t="n">
@@ -5935,6 +6316,11 @@
           <t>D076</t>
         </is>
       </c>
+      <c r="O80" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="23.85" customHeight="1" s="25">
       <c r="A81" s="36" t="n">
@@ -5994,6 +6380,11 @@
           <t>D077</t>
         </is>
       </c>
+      <c r="O81" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="23.85" customHeight="1" s="25">
       <c r="A82" s="36" t="n">
@@ -6053,6 +6444,11 @@
           <t>D078</t>
         </is>
       </c>
+      <c r="O82" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="23.85" customHeight="1" s="25">
       <c r="A83" s="36" t="n">
@@ -6112,6 +6508,11 @@
           <t>D079</t>
         </is>
       </c>
+      <c r="O83" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="23.85" customHeight="1" s="25">
       <c r="A84" s="36" t="n">
@@ -6171,6 +6572,11 @@
           <t>D080</t>
         </is>
       </c>
+      <c r="O84" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="23.85" customHeight="1" s="25">
       <c r="A85" s="36" t="n">
@@ -6230,6 +6636,11 @@
           <t>D081</t>
         </is>
       </c>
+      <c r="O85" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="23.85" customHeight="1" s="25">
       <c r="A86" s="36" t="n">
@@ -6289,6 +6700,11 @@
           <t>D082</t>
         </is>
       </c>
+      <c r="O86" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="23.85" customHeight="1" s="25">
       <c r="A87" s="36" t="n">
@@ -6348,6 +6764,11 @@
           <t>D083</t>
         </is>
       </c>
+      <c r="O87" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="23.85" customHeight="1" s="25">
       <c r="A88" s="36" t="n">
@@ -6407,6 +6828,11 @@
           <t>D084</t>
         </is>
       </c>
+      <c r="O88" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="23.85" customHeight="1" s="25">
       <c r="A89" s="36" t="n">
@@ -6466,6 +6892,11 @@
           <t>D085</t>
         </is>
       </c>
+      <c r="O89" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="23.85" customHeight="1" s="25">
       <c r="A90" s="45" t="n">
@@ -6525,6 +6956,11 @@
           <t>D086</t>
         </is>
       </c>
+      <c r="O90" s="24" t="inlineStr">
+        <is>
+          <t>5.0h</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.85" customHeight="1" s="25">
       <c r="A91" s="36" t="n">
@@ -6584,6 +7020,11 @@
           <t>D087</t>
         </is>
       </c>
+      <c r="O91" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="25">
       <c r="A92" s="36" t="n">
@@ -6643,6 +7084,11 @@
           <t>D088</t>
         </is>
       </c>
+      <c r="O92" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="25">
       <c r="A93" s="36" t="n">
@@ -6702,6 +7148,11 @@
           <t>D089</t>
         </is>
       </c>
+      <c r="O93" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="23.85" customHeight="1" s="25">
       <c r="A94" s="36" t="n">
@@ -6761,6 +7212,11 @@
           <t>D090</t>
         </is>
       </c>
+      <c r="O94" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="23.85" customHeight="1" s="25">
       <c r="A95" s="36" t="n">
@@ -6820,6 +7276,11 @@
           <t>D091</t>
         </is>
       </c>
+      <c r="O95" s="24" t="inlineStr">
+        <is>
+          <t>5.0h</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="25">
       <c r="A96" s="36" t="n">
@@ -6879,6 +7340,11 @@
           <t>D092</t>
         </is>
       </c>
+      <c r="O96" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="23.85" customHeight="1" s="25">
       <c r="A97" s="36" t="n">
@@ -6938,6 +7404,11 @@
           <t>D093</t>
         </is>
       </c>
+      <c r="O97" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="23.85" customHeight="1" s="25">
       <c r="A98" s="36" t="n">
@@ -6997,6 +7468,11 @@
           <t>D094</t>
         </is>
       </c>
+      <c r="O98" s="24" t="inlineStr">
+        <is>
+          <t>5.0h</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="23.85" customHeight="1" s="25">
       <c r="A99" s="36" t="n">
@@ -7056,6 +7532,11 @@
           <t>D095</t>
         </is>
       </c>
+      <c r="O99" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="25">
       <c r="A100" s="36" t="n">
@@ -7115,6 +7596,11 @@
           <t>D096</t>
         </is>
       </c>
+      <c r="O100" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="23.85" customHeight="1" s="25">
       <c r="A101" s="36" t="n">
@@ -7174,6 +7660,11 @@
           <t>D097</t>
         </is>
       </c>
+      <c r="O101" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="23.85" customHeight="1" s="25">
       <c r="A102" s="36" t="n">
@@ -7233,6 +7724,11 @@
           <t>D098</t>
         </is>
       </c>
+      <c r="O102" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="23.85" customHeight="1" s="25">
       <c r="A103" s="36" t="n">
@@ -7292,6 +7788,11 @@
           <t>D099</t>
         </is>
       </c>
+      <c r="O103" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="23.85" customHeight="1" s="25">
       <c r="A104" s="45" t="n">
@@ -7351,6 +7852,11 @@
           <t>D100</t>
         </is>
       </c>
+      <c r="O104" s="24" t="inlineStr">
+        <is>
+          <t>6.5h</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="23.85" customHeight="1" s="25">
       <c r="A105" s="36" t="n">
@@ -7410,6 +7916,11 @@
           <t>D101</t>
         </is>
       </c>
+      <c r="O105" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="23.85" customHeight="1" s="25">
       <c r="A106" s="36" t="n">
@@ -7469,6 +7980,11 @@
           <t>D102</t>
         </is>
       </c>
+      <c r="O106" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="23.85" customHeight="1" s="25">
       <c r="A107" s="36" t="n">
@@ -7528,6 +8044,11 @@
           <t>D103</t>
         </is>
       </c>
+      <c r="O107" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="25">
       <c r="A108" s="36" t="n">
@@ -7587,6 +8108,11 @@
           <t>D104</t>
         </is>
       </c>
+      <c r="O108" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="25">
       <c r="A109" s="36" t="n">
@@ -7646,6 +8172,11 @@
           <t>D105</t>
         </is>
       </c>
+      <c r="O109" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="25">
       <c r="A110" s="36" t="n">
@@ -7705,6 +8236,11 @@
           <t>D106</t>
         </is>
       </c>
+      <c r="O110" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="25">
       <c r="A111" s="36" t="n">
@@ -7764,6 +8300,11 @@
           <t>D107</t>
         </is>
       </c>
+      <c r="O111" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="25">
       <c r="A112" s="36" t="n">
@@ -7823,6 +8364,11 @@
           <t>D108</t>
         </is>
       </c>
+      <c r="O112" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="25">
       <c r="A113" s="36" t="n">
@@ -7882,6 +8428,11 @@
           <t>D109</t>
         </is>
       </c>
+      <c r="O113" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="23.85" customHeight="1" s="25">
       <c r="A114" s="36" t="n">
@@ -7941,6 +8492,11 @@
           <t>D110</t>
         </is>
       </c>
+      <c r="O114" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="23.85" customHeight="1" s="25">
       <c r="A115" s="36" t="n">
@@ -8000,6 +8556,11 @@
           <t>D111</t>
         </is>
       </c>
+      <c r="O115" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="23.85" customHeight="1" s="25">
       <c r="A116" s="36" t="n">
@@ -8059,6 +8620,11 @@
           <t>D112</t>
         </is>
       </c>
+      <c r="O116" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="25">
       <c r="A117" s="36" t="n">
@@ -8118,6 +8684,11 @@
           <t>D113</t>
         </is>
       </c>
+      <c r="O117" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="25">
       <c r="A118" s="36" t="n">
@@ -8177,6 +8748,11 @@
           <t>D114</t>
         </is>
       </c>
+      <c r="O118" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="25">
       <c r="A119" s="36" t="n">
@@ -8236,6 +8812,11 @@
           <t>D115</t>
         </is>
       </c>
+      <c r="O119" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="23.85" customHeight="1" s="25">
       <c r="A120" s="36" t="n">
@@ -8295,6 +8876,11 @@
           <t>D116</t>
         </is>
       </c>
+      <c r="O120" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="25">
       <c r="A121" s="36" t="n">
@@ -8354,6 +8940,11 @@
           <t>D117</t>
         </is>
       </c>
+      <c r="O121" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="23.85" customHeight="1" s="25">
       <c r="A122" s="36" t="n">
@@ -8413,6 +9004,11 @@
           <t>D118</t>
         </is>
       </c>
+      <c r="O122" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="25">
       <c r="A123" s="36" t="n">
@@ -8472,6 +9068,11 @@
           <t>D119</t>
         </is>
       </c>
+      <c r="O123" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="23.85" customHeight="1" s="25">
       <c r="A124" s="45" t="n">
@@ -8531,6 +9132,11 @@
           <t>D120</t>
         </is>
       </c>
+      <c r="O124" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="23.85" customHeight="1" s="25">
       <c r="A125" s="36" t="n">
@@ -8590,6 +9196,11 @@
           <t>D121</t>
         </is>
       </c>
+      <c r="O125" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="23.85" customHeight="1" s="25">
       <c r="A126" s="36" t="n">
@@ -8649,6 +9260,11 @@
           <t>D122</t>
         </is>
       </c>
+      <c r="O126" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="23.85" customHeight="1" s="25">
       <c r="A127" s="36" t="n">
@@ -8708,6 +9324,11 @@
           <t>D123</t>
         </is>
       </c>
+      <c r="O127" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="23.85" customHeight="1" s="25">
       <c r="A128" s="36" t="n">
@@ -8767,6 +9388,11 @@
           <t>D124</t>
         </is>
       </c>
+      <c r="O128" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="25">
       <c r="A129" s="36" t="n">
@@ -8826,6 +9452,11 @@
           <t>D125</t>
         </is>
       </c>
+      <c r="O129" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="25">
       <c r="A130" s="36" t="n">
@@ -8885,6 +9516,11 @@
           <t>D126</t>
         </is>
       </c>
+      <c r="O130" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="25">
       <c r="A131" s="36" t="n">
@@ -8944,6 +9580,11 @@
           <t>D127</t>
         </is>
       </c>
+      <c r="O131" s="24" t="inlineStr">
+        <is>
+          <t>5.0h</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="23.85" customHeight="1" s="25">
       <c r="A132" s="36" t="n">
@@ -9003,6 +9644,11 @@
           <t>D128</t>
         </is>
       </c>
+      <c r="O132" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="23.85" customHeight="1" s="25">
       <c r="A133" s="36" t="n">
@@ -9062,6 +9708,11 @@
           <t>D129</t>
         </is>
       </c>
+      <c r="O133" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="25">
       <c r="A134" s="36" t="n">
@@ -9121,6 +9772,11 @@
           <t>D130</t>
         </is>
       </c>
+      <c r="O134" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="25">
       <c r="A135" s="36" t="n">
@@ -9180,6 +9836,11 @@
           <t>D131</t>
         </is>
       </c>
+      <c r="O135" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="23.85" customHeight="1" s="25">
       <c r="A136" s="36" t="n">
@@ -9239,6 +9900,11 @@
           <t>D132</t>
         </is>
       </c>
+      <c r="O136" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="25">
       <c r="A137" s="36" t="n">
@@ -9298,6 +9964,11 @@
           <t>D133</t>
         </is>
       </c>
+      <c r="O137" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="23.85" customHeight="1" s="25">
       <c r="A138" s="36" t="n">
@@ -9357,6 +10028,11 @@
           <t>D134</t>
         </is>
       </c>
+      <c r="O138" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="25">
       <c r="A139" s="36" t="n">
@@ -9416,6 +10092,11 @@
           <t>D135</t>
         </is>
       </c>
+      <c r="O139" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="25">
       <c r="A140" s="39" t="n">
@@ -9475,6 +10156,11 @@
           <t>D136</t>
         </is>
       </c>
+      <c r="O140" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="25">
       <c r="A141" s="36" t="n">
@@ -9534,6 +10220,11 @@
           <t>D137</t>
         </is>
       </c>
+      <c r="O141" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="23.85" customHeight="1" s="25">
       <c r="A142" s="36" t="n">
@@ -9593,6 +10284,11 @@
           <t>D138</t>
         </is>
       </c>
+      <c r="O142" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="25">
       <c r="A143" s="36" t="n">
@@ -9652,6 +10348,11 @@
           <t>D139</t>
         </is>
       </c>
+      <c r="O143" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="25">
       <c r="A144" s="36" t="n">
@@ -9711,6 +10412,11 @@
           <t>D140</t>
         </is>
       </c>
+      <c r="O144" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="25">
       <c r="A145" s="36" t="n">
@@ -9770,6 +10476,11 @@
           <t>D141</t>
         </is>
       </c>
+      <c r="O145" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="25">
       <c r="A146" s="36" t="n">
@@ -9829,6 +10540,11 @@
           <t>D142</t>
         </is>
       </c>
+      <c r="O146" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="25">
       <c r="A147" s="36" t="n">
@@ -9888,6 +10604,11 @@
           <t>D143</t>
         </is>
       </c>
+      <c r="O147" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="25">
       <c r="A148" s="36" t="n">
@@ -9947,6 +10668,11 @@
           <t>D144</t>
         </is>
       </c>
+      <c r="O148" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="25">
       <c r="A149" s="36" t="n">
@@ -10006,6 +10732,11 @@
           <t>D145</t>
         </is>
       </c>
+      <c r="O149" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="25">
       <c r="A150" s="36" t="n">
@@ -10065,6 +10796,11 @@
           <t>D146</t>
         </is>
       </c>
+      <c r="O150" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="25">
       <c r="A151" s="36" t="n">
@@ -10124,6 +10860,11 @@
           <t>D147</t>
         </is>
       </c>
+      <c r="O151" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="25">
       <c r="A152" s="36" t="n">
@@ -10183,6 +10924,11 @@
           <t>D148</t>
         </is>
       </c>
+      <c r="O152" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="23.85" customHeight="1" s="25">
       <c r="A153" s="36" t="n">
@@ -10242,6 +10988,11 @@
           <t>D149</t>
         </is>
       </c>
+      <c r="O153" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="23.85" customHeight="1" s="25">
       <c r="A154" s="36" t="n">
@@ -10301,6 +11052,11 @@
           <t>D150</t>
         </is>
       </c>
+      <c r="O154" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="25">
       <c r="A155" s="36" t="n">
@@ -10360,6 +11116,11 @@
           <t>D151</t>
         </is>
       </c>
+      <c r="O155" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="25">
       <c r="A156" s="45" t="n">
@@ -10419,6 +11180,11 @@
           <t>D152</t>
         </is>
       </c>
+      <c r="O156" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="23.85" customHeight="1" s="25">
       <c r="A157" s="36" t="n">
@@ -10478,6 +11244,11 @@
           <t>D153</t>
         </is>
       </c>
+      <c r="O157" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="23.85" customHeight="1" s="25">
       <c r="A158" s="36" t="n">
@@ -10537,6 +11308,11 @@
           <t>D154</t>
         </is>
       </c>
+      <c r="O158" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="23.85" customHeight="1" s="25">
       <c r="A159" s="36" t="n">
@@ -10596,6 +11372,11 @@
           <t>D155</t>
         </is>
       </c>
+      <c r="O159" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="23.85" customHeight="1" s="25">
       <c r="A160" s="36" t="n">
@@ -10655,6 +11436,11 @@
           <t>D156</t>
         </is>
       </c>
+      <c r="O160" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="23.85" customHeight="1" s="25">
       <c r="A161" s="36" t="n">
@@ -10714,6 +11500,11 @@
           <t>D157</t>
         </is>
       </c>
+      <c r="O161" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="23.85" customHeight="1" s="25">
       <c r="A162" s="36" t="n">
@@ -10773,6 +11564,11 @@
           <t>D158</t>
         </is>
       </c>
+      <c r="O162" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="23.85" customHeight="1" s="25">
       <c r="A163" s="36" t="n">
@@ -10832,6 +11628,11 @@
           <t>D159</t>
         </is>
       </c>
+      <c r="O163" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="23.85" customHeight="1" s="25">
       <c r="A164" s="36" t="n">
@@ -10891,6 +11692,11 @@
           <t>D160</t>
         </is>
       </c>
+      <c r="O164" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="23.85" customHeight="1" s="25">
       <c r="A165" s="36" t="n">
@@ -10950,6 +11756,11 @@
           <t>D161</t>
         </is>
       </c>
+      <c r="O165" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="23.85" customHeight="1" s="25">
       <c r="A166" s="36" t="n">
@@ -11009,6 +11820,11 @@
           <t>D162</t>
         </is>
       </c>
+      <c r="O166" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="23.85" customHeight="1" s="25">
       <c r="A167" s="36" t="n">
@@ -11068,6 +11884,11 @@
           <t>D163</t>
         </is>
       </c>
+      <c r="O167" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="23.85" customHeight="1" s="25">
       <c r="A168" s="36" t="n">
@@ -11127,6 +11948,11 @@
           <t>D164</t>
         </is>
       </c>
+      <c r="O168" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="23.85" customHeight="1" s="25">
       <c r="A169" s="36" t="n">
@@ -11186,6 +12012,11 @@
           <t>D165</t>
         </is>
       </c>
+      <c r="O169" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="23.85" customHeight="1" s="25">
       <c r="A170" s="45" t="n">
@@ -11245,6 +12076,11 @@
           <t>D166</t>
         </is>
       </c>
+      <c r="O170" s="24" t="inlineStr">
+        <is>
+          <t>3.5h</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="23.85" customHeight="1" s="25">
       <c r="A171" s="36" t="n">
@@ -11304,6 +12140,11 @@
           <t>D167</t>
         </is>
       </c>
+      <c r="O171" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="25">
       <c r="A172" s="36" t="n">
@@ -11363,6 +12204,11 @@
           <t>D168</t>
         </is>
       </c>
+      <c r="O172" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="23.85" customHeight="1" s="25">
       <c r="A173" s="36" t="n">
@@ -11422,6 +12268,11 @@
           <t>D169</t>
         </is>
       </c>
+      <c r="O173" s="24" t="inlineStr">
+        <is>
+          <t>4.5h</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="23.85" customHeight="1" s="25">
       <c r="A174" s="36" t="n">
@@ -11481,6 +12332,11 @@
           <t>D170</t>
         </is>
       </c>
+      <c r="O174" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="23.85" customHeight="1" s="25">
       <c r="A175" s="36" t="n">
@@ -11540,6 +12396,11 @@
           <t>D171</t>
         </is>
       </c>
+      <c r="O175" s="24" t="inlineStr">
+        <is>
+          <t>4.0h</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15" customHeight="1" s="25">
       <c r="A176" s="36" t="n">
@@ -11599,6 +12460,11 @@
           <t>D172</t>
         </is>
       </c>
+      <c r="O176" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="23.85" customHeight="1" s="25">
       <c r="A177" s="36" t="n">
@@ -11658,6 +12524,11 @@
           <t>D173</t>
         </is>
       </c>
+      <c r="O177" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="23.85" customHeight="1" s="25">
       <c r="A178" s="36" t="n">
@@ -11717,6 +12588,11 @@
           <t>D174</t>
         </is>
       </c>
+      <c r="O178" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="25">
       <c r="A179" s="36" t="n">
@@ -11776,6 +12652,11 @@
           <t>D175</t>
         </is>
       </c>
+      <c r="O179" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="23.85" customHeight="1" s="25">
       <c r="A180" s="45" t="n">
@@ -11833,6 +12714,11 @@
       <c r="N180" s="44" t="inlineStr">
         <is>
           <t>D176</t>
+        </is>
+      </c>
+      <c r="O180" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
         </is>
       </c>
     </row>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1497,11 +1497,15 @@
       </c>
       <c r="J5" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K5" s="43" t="n"/>
-      <c r="L5" s="43" t="n"/>
+      <c r="L5" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D001.md)</t>
+        </is>
+      </c>
       <c r="M5" s="44" t="inlineStr">
         <is>
           <t>D001</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1565,11 +1565,15 @@
       </c>
       <c r="J6" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K6" s="43" t="n"/>
-      <c r="L6" s="43" t="n"/>
+      <c r="L6" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D002.md)</t>
+        </is>
+      </c>
       <c r="M6" s="44" t="inlineStr">
         <is>
           <t>D002</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1344,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O180"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="24" min="1" max="1"/>
@@ -12725,6 +12725,1350 @@
         </is>
       </c>
       <c r="O180" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="45" t="n">
+        <v>177</v>
+      </c>
+      <c r="B181" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A181-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C181" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D181" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E181" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F181" s="47" t="inlineStr">
+        <is>
+          <t>Schema: platform_users, support_access_grants, platform_role_changes, feature_flags</t>
+        </is>
+      </c>
+      <c r="G181" s="45" t="inlineStr">
+        <is>
+          <t>New tables per docs/design/03 (Platform administration); migration; explicit reviewed exclusion from the cross-tenant test generator</t>
+        </is>
+      </c>
+      <c r="H181" s="45" t="inlineStr">
+        <is>
+          <t>Migration applies cleanly; platform_users has no merchant_id; exclusion is an explicit annotation, not a silent skip</t>
+        </is>
+      </c>
+      <c r="I181" s="45" t="inlineStr">
+        <is>
+          <t>Confirm platform_users carries no merchant_id and no PII beyond email</t>
+        </is>
+      </c>
+      <c r="J181" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K181" s="43" t="n"/>
+      <c r="L181" s="43" t="n"/>
+      <c r="M181" s="44" t="inlineStr">
+        <is>
+          <t>D177</t>
+        </is>
+      </c>
+      <c r="N181" s="44" t="inlineStr">
+        <is>
+          <t>D177</t>
+        </is>
+      </c>
+      <c r="O181" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="45" t="n">
+        <v>178</v>
+      </c>
+      <c r="B182" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A182-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C182" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D182" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E182" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F182" s="47" t="inlineStr">
+        <is>
+          <t>Platform AuthProvider instance + mandatory MFA for all platform roles</t>
+        </is>
+      </c>
+      <c r="G182" s="45" t="inlineStr">
+        <is>
+          <t>AuthProvider (ADR-002) against platform_users; TOTP MFA enforced for all three platform roles</t>
+        </is>
+      </c>
+      <c r="H182" s="45" t="inlineStr">
+        <is>
+          <t>Login without completed MFA is rejected for every platform role, not only the top tier</t>
+        </is>
+      </c>
+      <c r="I182" s="45" t="inlineStr">
+        <is>
+          <t>Confirm MFA is enforced for PLATFORM_SUPPORT too, not only ADMIN/SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="J182" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K182" s="43" t="n"/>
+      <c r="L182" s="43" t="n"/>
+      <c r="M182" s="44" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="N182" s="44" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="O182" s="24" t="inlineStr">
+        <is>
+          <t>3.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="45" t="n">
+        <v>179</v>
+      </c>
+      <c r="B183" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A183-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C183" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D183" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E183" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F183" s="47" t="inlineStr">
+        <is>
+          <t>Break-glass grant workflow (backend)</t>
+        </is>
+      </c>
+      <c r="G183" s="45" t="inlineStr">
+        <is>
+          <t>support_access_grants create/expire/revoke; mandatory validated reason; fixed default expiry with a hard ceiling</t>
+        </is>
+      </c>
+      <c r="H183" s="45" t="inlineStr">
+        <is>
+          <t>A grant cannot be created without a validated reason; an expired grant is unusable without renewal</t>
+        </is>
+      </c>
+      <c r="I183" s="45" t="inlineStr">
+        <is>
+          <t>Confirm every merchant-data call checks for an active grant server-side, never client state</t>
+        </is>
+      </c>
+      <c r="J183" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K183" s="43" t="n"/>
+      <c r="L183" s="43" t="n"/>
+      <c r="M183" s="44" t="inlineStr">
+        <is>
+          <t>D179</t>
+        </is>
+      </c>
+      <c r="N183" s="44" t="inlineStr">
+        <is>
+          <t>D179</t>
+        </is>
+      </c>
+      <c r="O183" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="45" t="n">
+        <v>180</v>
+      </c>
+      <c r="B184" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A184-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C184" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D184" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E184" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F184" s="47" t="inlineStr">
+        <is>
+          <t>Audit log viewer UI</t>
+        </is>
+      </c>
+      <c r="G184" s="45" t="inlineStr">
+        <is>
+          <t>Read-only apps/admin view over audit_log with a manual hash-chain verification action</t>
+        </is>
+      </c>
+      <c r="H184" s="45" t="inlineStr">
+        <is>
+          <t>Viewer renders real audit rows; verification flags a deliberately corrupted test row</t>
+        </is>
+      </c>
+      <c r="I184" s="45" t="inlineStr">
+        <is>
+          <t>Confirm the viewer cannot mutate audit_log at the repository layer</t>
+        </is>
+      </c>
+      <c r="J184" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K184" s="43" t="n"/>
+      <c r="L184" s="43" t="n"/>
+      <c r="M184" s="44" t="inlineStr">
+        <is>
+          <t>D180</t>
+        </is>
+      </c>
+      <c r="N184" s="44" t="inlineStr">
+        <is>
+          <t>D180</t>
+        </is>
+      </c>
+      <c r="O184" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="45" t="n">
+        <v>181</v>
+      </c>
+      <c r="B185" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A185-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C185" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D185" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E185" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F185" s="47" t="inlineStr">
+        <is>
+          <t>apps/admin scaffold + network restriction — GATE G11 groundwork</t>
+        </is>
+      </c>
+      <c r="G185" s="45" t="inlineStr">
+        <is>
+          <t>New Next.js app per ADR-001; own hostname with IP allowlist or VPN/SSO gateway</t>
+        </is>
+      </c>
+      <c r="H185" s="45" t="inlineStr">
+        <is>
+          <t>apps/admin deploys independently; a request outside the allowlist is rejected before reaching the app</t>
+        </is>
+      </c>
+      <c r="I185" s="45" t="inlineStr">
+        <is>
+          <t>Confirm restriction is enforced at the infrastructure layer, not just documented</t>
+        </is>
+      </c>
+      <c r="J185" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K185" s="43" t="n"/>
+      <c r="L185" s="43" t="n"/>
+      <c r="M185" s="44" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="N185" s="44" t="inlineStr">
+        <is>
+          <t>D181</t>
+        </is>
+      </c>
+      <c r="O185" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="45" t="n">
+        <v>182</v>
+      </c>
+      <c r="B186" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A186-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C186" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D186" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E186" s="45" t="inlineStr">
+        <is>
+          <t>Platform auth &amp; break-glass</t>
+        </is>
+      </c>
+      <c r="F186" s="47" t="inlineStr">
+        <is>
+          <t>Support console: merchant/order/reservation lookup (read-only)</t>
+        </is>
+      </c>
+      <c r="G186" s="45" t="inlineStr">
+        <is>
+          <t>Search by merchant ID/slug/user email; loads data only inside an active grant</t>
+        </is>
+      </c>
+      <c r="H186" s="45" t="inlineStr">
+        <is>
+          <t>Lookup without an active grant is refused; lookup during a valid grant is audit-logged with the grant ID</t>
+        </is>
+      </c>
+      <c r="I186" s="45" t="inlineStr">
+        <is>
+          <t>Confirm search never free-text matches PII fields without a specific identifier</t>
+        </is>
+      </c>
+      <c r="J186" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K186" s="43" t="n"/>
+      <c r="L186" s="43" t="n"/>
+      <c r="M186" s="44" t="inlineStr">
+        <is>
+          <t>D182</t>
+        </is>
+      </c>
+      <c r="N186" s="44" t="inlineStr">
+        <is>
+          <t>D182</t>
+        </is>
+      </c>
+      <c r="O186" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="45" t="n">
+        <v>183</v>
+      </c>
+      <c r="B187" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A187-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C187" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D187" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E187" s="45" t="inlineStr">
+        <is>
+          <t>Support actions</t>
+        </is>
+      </c>
+      <c r="F187" s="47" t="inlineStr">
+        <is>
+          <t>Support action: void/refund an order</t>
+        </is>
+      </c>
+      <c r="G187" s="45" t="inlineStr">
+        <is>
+          <t>Routes through the existing payment service, grant-gated; no direct DB write</t>
+        </is>
+      </c>
+      <c r="H187" s="45" t="inlineStr">
+        <is>
+          <t>Refund from the console produces the same records as the merchant dashboard; fails outside a grant</t>
+        </is>
+      </c>
+      <c r="I187" s="45" t="inlineStr">
+        <is>
+          <t>Confirm deposit/capture-bounds invariants are not bypassed by this entry point</t>
+        </is>
+      </c>
+      <c r="J187" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K187" s="43" t="n"/>
+      <c r="L187" s="43" t="n"/>
+      <c r="M187" s="44" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="N187" s="44" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="O187" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="45" t="n">
+        <v>184</v>
+      </c>
+      <c r="B188" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A188-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C188" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D188" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E188" s="45" t="inlineStr">
+        <is>
+          <t>Support actions</t>
+        </is>
+      </c>
+      <c r="F188" s="47" t="inlineStr">
+        <is>
+          <t>Support action: release a stuck reservation</t>
+        </is>
+      </c>
+      <c r="G188" s="45" t="inlineStr">
+        <is>
+          <t>Forces a HELD/CONFIRMED reservation to CANCELLED outside its normal lifecycle, grant-gated</t>
+        </is>
+      </c>
+      <c r="H188" s="45" t="inlineStr">
+        <is>
+          <t>Releasing frees the slot for rebooking and is audit-logged with before/after state</t>
+        </is>
+      </c>
+      <c r="I188" s="45" t="inlineStr">
+        <is>
+          <t>Confirm this bypass is reachable only through this action</t>
+        </is>
+      </c>
+      <c r="J188" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K188" s="43" t="n"/>
+      <c r="L188" s="43" t="n"/>
+      <c r="M188" s="44" t="inlineStr">
+        <is>
+          <t>D184</t>
+        </is>
+      </c>
+      <c r="N188" s="44" t="inlineStr">
+        <is>
+          <t>D184</t>
+        </is>
+      </c>
+      <c r="O188" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="45" t="n">
+        <v>185</v>
+      </c>
+      <c r="B189" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A189-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C189" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D189" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E189" s="45" t="inlineStr">
+        <is>
+          <t>Support actions</t>
+        </is>
+      </c>
+      <c r="F189" s="47" t="inlineStr">
+        <is>
+          <t>Support action: resend notification / replay webhook event</t>
+        </is>
+      </c>
+      <c r="G189" s="45" t="inlineStr">
+        <is>
+          <t>Re-triggers a notification or replays a stored webhook event, grant-gated</t>
+        </is>
+      </c>
+      <c r="H189" s="45" t="inlineStr">
+        <is>
+          <t>Resend/replay produces the expected effect exactly once (idempotent) and is audit-logged</t>
+        </is>
+      </c>
+      <c r="I189" s="45" t="inlineStr">
+        <is>
+          <t>Confirm a replay cannot double-apply a financial side effect</t>
+        </is>
+      </c>
+      <c r="J189" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K189" s="43" t="n"/>
+      <c r="L189" s="43" t="n"/>
+      <c r="M189" s="44" t="inlineStr">
+        <is>
+          <t>D185</t>
+        </is>
+      </c>
+      <c r="N189" s="44" t="inlineStr">
+        <is>
+          <t>D185</t>
+        </is>
+      </c>
+      <c r="O189" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="45" t="n">
+        <v>186</v>
+      </c>
+      <c r="B190" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A190-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C190" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D190" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E190" s="45" t="inlineStr">
+        <is>
+          <t>Support actions</t>
+        </is>
+      </c>
+      <c r="F190" s="47" t="inlineStr">
+        <is>
+          <t>Support action audit trail + merchant-visible support-access notice</t>
+        </is>
+      </c>
+      <c r="G190" s="45" t="inlineStr">
+        <is>
+          <t>Every Epic B action queryable by grant ID; merchant dashboard addition surfacing support access</t>
+        </is>
+      </c>
+      <c r="H190" s="45" t="inlineStr">
+        <is>
+          <t>A merchant OWNER sees a real support-access event within one refresh</t>
+        </is>
+      </c>
+      <c r="I190" s="45" t="inlineStr">
+        <is>
+          <t>Confirm the notice cannot be suppressed by the platform user who created the grant</t>
+        </is>
+      </c>
+      <c r="J190" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K190" s="43" t="n"/>
+      <c r="L190" s="43" t="n"/>
+      <c r="M190" s="44" t="inlineStr">
+        <is>
+          <t>D186</t>
+        </is>
+      </c>
+      <c r="N190" s="44" t="inlineStr">
+        <is>
+          <t>D186</t>
+        </is>
+      </c>
+      <c r="O190" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="45" t="n">
+        <v>187</v>
+      </c>
+      <c r="B191" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A191-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C191" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D191" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E191" s="45" t="inlineStr">
+        <is>
+          <t>Merchant lifecycle</t>
+        </is>
+      </c>
+      <c r="F191" s="47" t="inlineStr">
+        <is>
+          <t>Merchant suspend workflow</t>
+        </is>
+      </c>
+      <c r="G191" s="45" t="inlineStr">
+        <is>
+          <t>PLATFORM_ADMIN+ suspends a merchant: storefront takedown, mandatory reason, notifies OWNERs</t>
+        </is>
+      </c>
+      <c r="H191" s="45" t="inlineStr">
+        <is>
+          <t>Suspended storefront returns unavailable within seconds; OWNERs notified; action audit-logged</t>
+        </is>
+      </c>
+      <c r="I191" s="45" t="inlineStr">
+        <is>
+          <t>Confirm a suspended merchant's existing sessions cannot complete a new checkout</t>
+        </is>
+      </c>
+      <c r="J191" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K191" s="43" t="n"/>
+      <c r="L191" s="43" t="n"/>
+      <c r="M191" s="44" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="N191" s="44" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="O191" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="45" t="n">
+        <v>188</v>
+      </c>
+      <c r="B192" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A192-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C192" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D192" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E192" s="45" t="inlineStr">
+        <is>
+          <t>Merchant lifecycle</t>
+        </is>
+      </c>
+      <c r="F192" s="47" t="inlineStr">
+        <is>
+          <t>Merchant reinstate workflow (dual control)</t>
+        </is>
+      </c>
+      <c r="G192" s="45" t="inlineStr">
+        <is>
+          <t>PLATFORM_SUPERADMIN-only reinstatement — the suspending role cannot reverse it alone</t>
+        </is>
+      </c>
+      <c r="H192" s="45" t="inlineStr">
+        <is>
+          <t>PLATFORM_ADMIN attempting to reinstate is refused; SUPERADMIN reinstatement restores the storefront</t>
+        </is>
+      </c>
+      <c r="I192" s="45" t="inlineStr">
+        <is>
+          <t>Confirm dual control is enforced server-side, not just a disabled button</t>
+        </is>
+      </c>
+      <c r="J192" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K192" s="43" t="n"/>
+      <c r="L192" s="43" t="n"/>
+      <c r="M192" s="44" t="inlineStr">
+        <is>
+          <t>D188</t>
+        </is>
+      </c>
+      <c r="N192" s="44" t="inlineStr">
+        <is>
+          <t>D188</t>
+        </is>
+      </c>
+      <c r="O192" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="45" t="n">
+        <v>189</v>
+      </c>
+      <c r="B193" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A193-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C193" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D193" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E193" s="45" t="inlineStr">
+        <is>
+          <t>Merchant lifecycle</t>
+        </is>
+      </c>
+      <c r="F193" s="47" t="inlineStr">
+        <is>
+          <t>Merchant onboard/offboard admin view</t>
+        </is>
+      </c>
+      <c r="G193" s="45" t="inlineStr">
+        <is>
+          <t>Create merchant record + OWNER invitation; offboard triggers existing retention rules (08)</t>
+        </is>
+      </c>
+      <c r="H193" s="45" t="inlineStr">
+        <is>
+          <t>New merchant completes OWNER signup from invitation; offboarding matches 08 exactly</t>
+        </is>
+      </c>
+      <c r="I193" s="45" t="inlineStr">
+        <is>
+          <t>Confirm offboarding does not delete financial/audit records</t>
+        </is>
+      </c>
+      <c r="J193" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K193" s="43" t="n"/>
+      <c r="L193" s="43" t="n"/>
+      <c r="M193" s="44" t="inlineStr">
+        <is>
+          <t>D189</t>
+        </is>
+      </c>
+      <c r="N193" s="44" t="inlineStr">
+        <is>
+          <t>D189</t>
+        </is>
+      </c>
+      <c r="O193" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="45" t="n">
+        <v>190</v>
+      </c>
+      <c r="B194" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A194-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C194" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D194" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E194" s="45" t="inlineStr">
+        <is>
+          <t>Merchant lifecycle</t>
+        </is>
+      </c>
+      <c r="F194" s="47" t="inlineStr">
+        <is>
+          <t>Merchant lifecycle audit + notifications</t>
+        </is>
+      </c>
+      <c r="G194" s="45" t="inlineStr">
+        <is>
+          <t>Consolidates suspend/reinstate/onboard/offboard into one auditable event stream</t>
+        </is>
+      </c>
+      <c r="H194" s="45" t="inlineStr">
+        <is>
+          <t>Lifecycle transitions for a test merchant appear in the audit log in correct order</t>
+        </is>
+      </c>
+      <c r="I194" s="45" t="inlineStr">
+        <is>
+          <t>Confirm lifecycle events cannot be reordered or backdated by client timestamps</t>
+        </is>
+      </c>
+      <c r="J194" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K194" s="43" t="n"/>
+      <c r="L194" s="43" t="n"/>
+      <c r="M194" s="44" t="inlineStr">
+        <is>
+          <t>D190</t>
+        </is>
+      </c>
+      <c r="N194" s="44" t="inlineStr">
+        <is>
+          <t>D190</t>
+        </is>
+      </c>
+      <c r="O194" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="45" t="n">
+        <v>191</v>
+      </c>
+      <c r="B195" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A195-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C195" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D195" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E195" s="45" t="inlineStr">
+        <is>
+          <t>Platform reporting</t>
+        </is>
+      </c>
+      <c r="F195" s="47" t="inlineStr">
+        <is>
+          <t>Platform-wide aggregate reporting queries</t>
+        </is>
+      </c>
+      <c r="G195" s="45" t="inlineStr">
+        <is>
+          <t>GMV, active merchants, booking volume by mode, take-rate revenue, deposit/claim rates — aggregate only</t>
+        </is>
+      </c>
+      <c r="H195" s="45" t="inlineStr">
+        <is>
+          <t>Queries return correct aggregates against seeded multi-merchant data; no row-level PII returned</t>
+        </is>
+      </c>
+      <c r="I195" s="45" t="inlineStr">
+        <is>
+          <t>Confirm anything needing a specific customer/order goes through the grant workflow</t>
+        </is>
+      </c>
+      <c r="J195" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K195" s="43" t="n"/>
+      <c r="L195" s="43" t="n"/>
+      <c r="M195" s="44" t="inlineStr">
+        <is>
+          <t>D191</t>
+        </is>
+      </c>
+      <c r="N195" s="44" t="inlineStr">
+        <is>
+          <t>D191</t>
+        </is>
+      </c>
+      <c r="O195" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="45" t="n">
+        <v>192</v>
+      </c>
+      <c r="B196" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A196-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C196" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D196" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E196" s="45" t="inlineStr">
+        <is>
+          <t>Platform reporting</t>
+        </is>
+      </c>
+      <c r="F196" s="47" t="inlineStr">
+        <is>
+          <t>Reporting dashboard UI</t>
+        </is>
+      </c>
+      <c r="G196" s="45" t="inlineStr">
+        <is>
+          <t>apps/admin views for Epic D aggregates — charts/tables, date-range filtering</t>
+        </is>
+      </c>
+      <c r="H196" s="45" t="inlineStr">
+        <is>
+          <t>Dashboard renders real aggregate data; filtering changes results correctly</t>
+        </is>
+      </c>
+      <c r="I196" s="45" t="inlineStr">
+        <is>
+          <t>Confirm the dashboard calls only aggregate endpoints, never raw per-merchant data</t>
+        </is>
+      </c>
+      <c r="J196" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K196" s="43" t="n"/>
+      <c r="L196" s="43" t="n"/>
+      <c r="M196" s="44" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="N196" s="44" t="inlineStr">
+        <is>
+          <t>D192</t>
+        </is>
+      </c>
+      <c r="O196" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="45" t="n">
+        <v>193</v>
+      </c>
+      <c r="B197" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A197-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C197" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D197" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E197" s="45" t="inlineStr">
+        <is>
+          <t>Platform reporting</t>
+        </is>
+      </c>
+      <c r="F197" s="47" t="inlineStr">
+        <is>
+          <t>Scheduled CSV export</t>
+        </is>
+      </c>
+      <c r="G197" s="45" t="inlineStr">
+        <is>
+          <t>On-demand and scheduled CSV export of Epic D aggregates</t>
+        </is>
+      </c>
+      <c r="H197" s="45" t="inlineStr">
+        <is>
+          <t>Exported CSV matches dashboard numbers for the same range; export is audit-logged</t>
+        </is>
+      </c>
+      <c r="I197" s="45" t="inlineStr">
+        <is>
+          <t>Confirm exports contain aggregates only, no row-level PII</t>
+        </is>
+      </c>
+      <c r="J197" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K197" s="43" t="n"/>
+      <c r="L197" s="43" t="n"/>
+      <c r="M197" s="44" t="inlineStr">
+        <is>
+          <t>D193</t>
+        </is>
+      </c>
+      <c r="N197" s="44" t="inlineStr">
+        <is>
+          <t>D193</t>
+        </is>
+      </c>
+      <c r="O197" s="24" t="inlineStr">
+        <is>
+          <t>1.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="45" t="n">
+        <v>194</v>
+      </c>
+      <c r="B198" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A198-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C198" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D198" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E198" s="45" t="inlineStr">
+        <is>
+          <t>Feature flags &amp; role management</t>
+        </is>
+      </c>
+      <c r="F198" s="47" t="inlineStr">
+        <is>
+          <t>Feature flag schema + service</t>
+        </is>
+      </c>
+      <c r="G198" s="45" t="inlineStr">
+        <is>
+          <t>feature_flags/feature_flag_overrides; packages/config reads global default plus per-merchant override</t>
+        </is>
+      </c>
+      <c r="H198" s="45" t="inlineStr">
+        <is>
+          <t>Toggling globally changes behavior without an override; per-merchant override takes precedence</t>
+        </is>
+      </c>
+      <c r="I198" s="45" t="inlineStr">
+        <is>
+          <t>Confirm flag reads cannot serve a stale override past a short bounded TTL</t>
+        </is>
+      </c>
+      <c r="J198" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K198" s="43" t="n"/>
+      <c r="L198" s="43" t="n"/>
+      <c r="M198" s="44" t="inlineStr">
+        <is>
+          <t>D194</t>
+        </is>
+      </c>
+      <c r="N198" s="44" t="inlineStr">
+        <is>
+          <t>D194</t>
+        </is>
+      </c>
+      <c r="O198" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="45" t="n">
+        <v>195</v>
+      </c>
+      <c r="B199" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A199-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C199" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D199" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E199" s="45" t="inlineStr">
+        <is>
+          <t>Feature flags &amp; role management</t>
+        </is>
+      </c>
+      <c r="F199" s="47" t="inlineStr">
+        <is>
+          <t>Feature flag management UI</t>
+        </is>
+      </c>
+      <c r="G199" s="45" t="inlineStr">
+        <is>
+          <t>PLATFORM_ADMIN+ view to toggle flags globally or per-merchant</t>
+        </is>
+      </c>
+      <c r="H199" s="45" t="inlineStr">
+        <is>
+          <t>A toggle is reflected within the TTL window and is audit-logged with before/after state</t>
+        </is>
+      </c>
+      <c r="I199" s="45" t="inlineStr">
+        <is>
+          <t>Confirm only PLATFORM_ADMIN+ can toggle flags</t>
+        </is>
+      </c>
+      <c r="J199" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K199" s="43" t="n"/>
+      <c r="L199" s="43" t="n"/>
+      <c r="M199" s="44" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="N199" s="44" t="inlineStr">
+        <is>
+          <t>D195</t>
+        </is>
+      </c>
+      <c r="O199" s="24" t="inlineStr">
+        <is>
+          <t>2.0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="45" t="n">
+        <v>196</v>
+      </c>
+      <c r="B200" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A200-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C200" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D200" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E200" s="45" t="inlineStr">
+        <is>
+          <t>Feature flags &amp; role management</t>
+        </is>
+      </c>
+      <c r="F200" s="47" t="inlineStr">
+        <is>
+          <t>Platform staff role/permission management UI</t>
+        </is>
+      </c>
+      <c r="G200" s="45" t="inlineStr">
+        <is>
+          <t>PLATFORM_SUPERADMIN-only: create/deactivate platform_users, assign roles; notifies all SUPERADMINs</t>
+        </is>
+      </c>
+      <c r="H200" s="45" t="inlineStr">
+        <is>
+          <t>Role change by a SUPERADMIN succeeds and notifies every other SUPERADMIN; refused for non-SUPERADMIN</t>
+        </is>
+      </c>
+      <c r="I200" s="45" t="inlineStr">
+        <is>
+          <t>Confirm a platform user cannot escalate their own role unilaterally</t>
+        </is>
+      </c>
+      <c r="J200" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K200" s="43" t="n"/>
+      <c r="L200" s="43" t="n"/>
+      <c r="M200" s="44" t="inlineStr">
+        <is>
+          <t>D196</t>
+        </is>
+      </c>
+      <c r="N200" s="44" t="inlineStr">
+        <is>
+          <t>D196</t>
+        </is>
+      </c>
+      <c r="O200" s="24" t="inlineStr">
+        <is>
+          <t>2.5h</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="45" t="n">
+        <v>197</v>
+      </c>
+      <c r="B201" s="46">
+        <f>WORKDAY(Config!$B$5,ROUND((A201-1)*5/Config!$B$6,0))</f>
+        <v/>
+      </c>
+      <c r="C201" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D201" s="45" t="inlineStr">
+        <is>
+          <t>Platform Admin Console</t>
+        </is>
+      </c>
+      <c r="E201" s="45" t="inlineStr">
+        <is>
+          <t>Feature flags &amp; role management</t>
+        </is>
+      </c>
+      <c r="F201" s="47" t="inlineStr">
+        <is>
+          <t>Platform admin console review — GATE G11</t>
+        </is>
+      </c>
+      <c r="G201" s="45" t="inlineStr">
+        <is>
+          <t>Full review against 16: grant-scoping test suite, audit-row-per-action test, network-restriction verification</t>
+        </is>
+      </c>
+      <c r="H201" s="45" t="inlineStr">
+        <is>
+          <t>G11 test proves no merchant-data access without an active grant; every mutating action produces a traceable audit row</t>
+        </is>
+      </c>
+      <c r="I201" s="45" t="inlineStr">
+        <is>
+          <t>Confirm dual-control and MFA-for-all-platform-roles are both actually tested</t>
+        </is>
+      </c>
+      <c r="J201" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K201" s="43" t="n"/>
+      <c r="L201" s="43" t="n"/>
+      <c r="M201" s="44" t="inlineStr">
+        <is>
+          <t>D197</t>
+        </is>
+      </c>
+      <c r="N201" s="44" t="inlineStr">
+        <is>
+          <t>D197</t>
+        </is>
+      </c>
+      <c r="O201" s="24" t="inlineStr">
         <is>
           <t>3.0h</t>
         </is>
@@ -13090,6 +14434,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N179" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId351"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N180" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N181" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N182" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N183" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N184" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N185" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N186" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N187" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N188" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N189" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N190" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N191" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N192" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N193" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N194" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N195" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N196" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N197" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N198" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N199" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N200" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N201" r:id="rId394"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1633,11 +1633,15 @@
       </c>
       <c r="J7" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K7" s="43" t="n"/>
-      <c r="L7" s="43" t="n"/>
+      <c r="L7" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D003.md)</t>
+        </is>
+      </c>
       <c r="M7" s="44" t="inlineStr">
         <is>
           <t>D003</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1701,11 +1701,15 @@
       </c>
       <c r="J8" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K8" s="43" t="n"/>
-      <c r="L8" s="43" t="n"/>
+      <c r="L8" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D004.md)</t>
+        </is>
+      </c>
       <c r="M8" s="44" t="inlineStr">
         <is>
           <t>D004</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1769,11 +1769,15 @@
       </c>
       <c r="J9" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K9" s="43" t="n"/>
-      <c r="L9" s="43" t="n"/>
+      <c r="L9" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D005.md)</t>
+        </is>
+      </c>
       <c r="M9" s="44" t="inlineStr">
         <is>
           <t>D005</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1837,11 +1837,15 @@
       </c>
       <c r="J10" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K10" s="43" t="n"/>
-      <c r="L10" s="43" t="n"/>
+      <c r="L10" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D006.md)</t>
+        </is>
+      </c>
       <c r="M10" s="44" t="inlineStr">
         <is>
           <t>D006</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1905,11 +1905,15 @@
       </c>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K11" s="43" t="n"/>
-      <c r="L11" s="43" t="n"/>
+      <c r="L11" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D007.md)</t>
+        </is>
+      </c>
       <c r="M11" s="44" t="inlineStr">
         <is>
           <t>D007</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -1973,11 +1973,15 @@
       </c>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K12" s="43" t="n"/>
-      <c r="L12" s="43" t="n"/>
+      <c r="L12" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D008.md)</t>
+        </is>
+      </c>
       <c r="M12" s="44" t="inlineStr">
         <is>
           <t>D008</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -2041,11 +2041,15 @@
       </c>
       <c r="J13" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K13" s="43" t="n"/>
-      <c r="L13" s="43" t="n"/>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D009.md)</t>
+        </is>
+      </c>
       <c r="M13" s="44" t="inlineStr">
         <is>
           <t>D009</t>
@@ -2105,13 +2109,13 @@
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Carried</t>
         </is>
       </c>
       <c r="K14" s="43" t="n"/>
       <c r="L14" s="43" t="inlineStr">
         <is>
-          <t>Revised per ADR-002 (2026-09-07): was 'Identity provider spike / OIDC PKCE'. Founder decision: native auth now, Auth0-ready interface, Auth0 wired in later.</t>
+          <t>[log](docs/logs/D010.md)</t>
         </is>
       </c>
       <c r="M14" s="44" t="inlineStr">

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -2109,7 +2109,7 @@
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Carried</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="43" t="n"/>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -2041,11 +2041,15 @@
       </c>
       <c r="J13" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K13" s="43" t="n"/>
-      <c r="L13" s="43" t="n"/>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D009.md)</t>
+        </is>
+      </c>
       <c r="M13" s="44" t="inlineStr">
         <is>
           <t>D009</t>
@@ -2105,13 +2109,13 @@
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="43" t="n"/>
       <c r="L14" s="43" t="inlineStr">
         <is>
-          <t>Revised per ADR-002 (2026-09-07): was 'Identity provider spike / OIDC PKCE'. Founder decision: native auth now, Auth0-ready interface, Auth0 wired in later.</t>
+          <t>[log](docs/logs/D010.md)</t>
         </is>
       </c>
       <c r="M14" s="44" t="inlineStr">
@@ -2173,11 +2177,15 @@
       </c>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K15" s="43" t="n"/>
-      <c r="L15" s="43" t="n"/>
+      <c r="L15" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D011.md)</t>
+        </is>
+      </c>
       <c r="M15" s="44" t="inlineStr">
         <is>
           <t>D011</t>

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -2041,11 +2041,15 @@
       </c>
       <c r="J13" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K13" s="43" t="n"/>
-      <c r="L13" s="43" t="n"/>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D009.md)</t>
+        </is>
+      </c>
       <c r="M13" s="44" t="inlineStr">
         <is>
           <t>D009</t>
@@ -2105,13 +2109,13 @@
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="43" t="n"/>
       <c r="L14" s="43" t="inlineStr">
         <is>
-          <t>Revised per ADR-002 (2026-09-07): was 'Identity provider spike / OIDC PKCE'. Founder decision: native auth now, Auth0-ready interface, Auth0 wired in later.</t>
+          <t>[log](docs/logs/D010.md)</t>
         </is>
       </c>
       <c r="M14" s="44" t="inlineStr">

--- a/docs/implementation_calendar/build_calendar.xlsx
+++ b/docs/implementation_calendar/build_calendar.xlsx
@@ -2177,11 +2177,15 @@
       </c>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K15" s="43" t="n"/>
-      <c r="L15" s="43" t="n"/>
+      <c r="L15" s="43" t="inlineStr">
+        <is>
+          <t>[log](docs/logs/D011.md)</t>
+        </is>
+      </c>
       <c r="M15" s="44" t="inlineStr">
         <is>
           <t>D011</t>
